--- a/design/demo/首版.xlsx
+++ b/design/demo/首版.xlsx
@@ -71,18 +71,801 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/comments/fieldNotes1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 Item 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史首版沿用 1=装备、4=普通道具、10=值类型货币。本工作簿的撤离战利品使用 4，不套用当前正式表的 5=战利品。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史首版按 Kind 解释小类，0 表示未细分。示例装备使用 Type=1 表示武器，不套用当前工具或弹药分类。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史首版的装备示例填 7 表示枪械，0 表示未细分。此值需与 Kind、Type 组合解释，不按 ID 数字位推断。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史首版单格堆叠上限，装备固定为 1，示例战利品至少为 1。掉落超过上限时拆堆并保留余数；旧值类型货币的 0 约定不用于本版战利品。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 MonsterSkill 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Monster.MonsterIdx，选择怪物基础配置。同一种怪物可由多个不同 SpawnIdx 的出生点生成。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史首版引用 Skill.SkillIdx，怪物使用 CastType=2 的近战招式。回归入口要求每种引用的怪物恰好绑定一个攻击技能。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+旧设计预留从小到大尝试技能的优先级。历史首版实际要求每怪恰好一个技能，不能据此认为该回归入口支持多技能轮转。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 Weapon 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史首版引用 Skill.SkillIdx，集中维护射程、伤害与射击冷却。固定步枪要求 CastType=1，且前摇和后摇均为 0。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+枪内可装填的最大弹数，与 InitialReserve 的备弹分开记录。一次射击消耗一发弹药，多弹丸射击也只扣一发。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+开局携带的备用弹药数量，不包括枪内弹匣。换弹从备弹转移到弹匣，不会凭空补充弹药。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史首版一次换弹的耗时，单位为 Tick，60 Tick=1 秒。该旧表没有 ReloadType，不套用当前正式版逐轮装填的规则。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes12.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 Skill 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史首版 1=射线伤害、2=近战单次伤害，二者均针对敌方。射线考虑最近命中和墙体遮挡，近战需满足距离与空间相交。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史招式的攻击距离，单位为毫米。枪械和怪物通过技能引用共用该数值，怪物警戒范围不得小于其近战距离。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史招式的一次基础伤害，枪械和怪物都从所引用技能读取。命中前仍需通过距离与墙体遮挡等实际判定。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史招式从起手开始计算的冷却，单位为 Tick。旧回归校验同样要求前摇加后摇严格小于冷却，未命中也消耗本次冷却。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史招式起手到尝试命中的前摇，单位为 Tick。前摇结束时重新检查目标；射线步枪要求为 0，Boss 近战可配置预警时间。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史招式命中尝试后的后摇，单位为 Tick。与前摇之和必须严格小于冷却，射线步枪要求为 0。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes13.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 Drop 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 DropEntry 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Drop.DropIdx，由 DropEntry 中相同 DropIdx 的多行共同组成掉落组。一个组可被多个怪物复用。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Item.ItemIdx，表示本行可能掉落的物品。同一 DropIdx 下同一种物品只配置一行；历史首版仅掉落 Kind=4 的普通道具。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+每行独立判定的万分比概率，不是奖池权重。同组概率无需合计为 10000；10000 必掉、0 不掉，6000 表示 60%。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行概率判定成功后，在 [MinCount, MaxCount] 的整数闭区间内等概率取数量。至少为 1；与 MaxCount 相等时表示固定数量。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+掉落数量上限，必须大于或等于 MinCount。超过物品 MaxStack 时拆成多堆，余数保留；数量上限还会参与最坏情况的掉落容量校验。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes15.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 Bag 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+局内战利品背包的格数，当前实现范围为 1～32。相同物品按 MaxStack 合堆，超出的数量占用更多格子。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+玩家可拾取地面战利品的距离阈值，单位为毫米。它影响拾取判定，不改变物品堆叠上限或背包格数。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+主键同时引用 Item.ItemIdx，关联物品共同属性；本表补充装备与武器关联。当前历史首版用法要求物品 Kind=1，不能另编一个无对应物品的 ID。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史装备位置枚举中 1=武器，旧划线的 12/13 不采用。首版固定步枪按武器配置，其他位置为历史保留分类。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史首版固定枪械填写 7，原 1～6 为保留枚举。WeaponIdx 必须关联固定步枪配置，不因保留其他枚举就认为其行为已实现。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Weapon.WeaponIdx，连接装备物品与枪械行为。物品 ID 与武器配置 ID 属于不同命名空间，必须显式关联。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 Map 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+旧设计区分 1=灰盒清怪、2=撤离模式。历史首版只读取地图 2，且要求 Mode=2。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+地图边界尺寸，单位为毫米，1000 毫米=1 米。地图横向为 [0, Width]、纵向为 [0, Height]，碰撞与出生需在边界内。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+地图边界尺寸，单位为毫米，1000 毫米=1 米。地图横向为 [0, Width]、纵向为 [0, Height]，碰撞与出生需在边界内。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+每 Tick 向下增加的速度幅值，单位为毫米/Tick²。固定 60 Tick/秒；它不是以秒为单位的重力加速度。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 MapSolid 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Map.MapIdx，决定该行属于哪张地图。地图、碰撞块、出生点的 ID 各自独立，不按数字位推断归属。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形左下角坐标，单位为毫米，X 向右、Y 向上。区域右上角为 (X+W, Y+H)，须与出生点的脚底中心坐标区别。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形左下角坐标，单位为毫米，X 向右、Y 向上。区域右上角为 (X+W, Y+H)，须与出生点的脚底中心坐标区别。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形的宽或高，单位为毫米，必须为正数。与左下角 X、Y 共同定义区域，X+W、Y+H 不得超出地图边界。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形的宽或高，单位为毫米，必须为正数。与左下角 X、Y 共同定义区域，X+W、Y+H 不得超出地图边界。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+标识一个出生配置实例，与角色/怪物配置 ID 及运行时实体 ID 分开。多个出生点可以引用同一种角色配置；撤离条件引用怪物出生实例。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Map.MapIdx，决定该行属于哪张地图。地图、碰撞块、出生点的 ID 各自独立，不按数字位推断归属。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Player.PlayerIdx，选择角色基础配置。此 ID 不表示本局玩家实体，也不使用名称作为关联键。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Equip.ItemIdx，再通过 Equip.WeaponIdx 找到枪械配置。此处填写装备物品 ID，不直接填写 WeaponIdx。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+出生位置使用脚底中心坐标，单位为毫米，X 向右、Y 向上。不能将其当作碰撞矩形左下角，检查出生空间时还需计入角色宽高。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+出生位置使用脚底中心坐标，单位为毫米，X 向右、Y 向上。不能将其当作碰撞矩形左下角，检查出生空间时还需计入角色宽高。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+标识一个出生配置实例，与角色/怪物配置 ID 及运行时实体 ID 分开。多个出生点可以引用同一种角色配置；撤离条件引用怪物出生实例。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Map.MapIdx，决定该行属于哪张地图。地图、碰撞块、出生点的 ID 各自独立，不按数字位推断归属。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Monster.MonsterIdx，选择怪物基础配置。同一种怪物可由多个不同 SpawnIdx 的出生点生成。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+出生位置使用脚底中心坐标，单位为毫米，X 向右、Y 向上。不能将其当作碰撞矩形左下角，检查出生空间时还需计入角色宽高。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+出生位置使用脚底中心坐标，单位为毫米，X 向右、Y 向上。不能将其当作碰撞矩形左下角，检查出生空间时还需计入角色宽高。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+怪物脚底中心的巡逻左端 X 坐标，单位为毫米。须与 PatrolMax 组成有效区间，并为怪物半宽及连续地面支撑留出空间。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+怪物脚底中心的巡逻右端 X 坐标，单位为毫米。不得小于 PatrolMin；整个巡逻区域需避免穿墙、悬空和越界。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 ExtractPoint 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Map.MapIdx，决定该行属于哪张地图。地图、碰撞块、出生点的 ID 各自独立，不按数字位推断归属。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形左下角坐标，单位为毫米，X 向右、Y 向上。区域右上角为 (X+W, Y+H)，须与出生点的脚底中心坐标区别。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形左下角坐标，单位为毫米，X 向右、Y 向上。区域右上角为 (X+W, Y+H)，须与出生点的脚底中心坐标区别。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形的宽或高，单位为毫米，必须为正数。与左下角 X、Y 共同定义区域，X+W、Y+H 不得超出地图边界。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+矩形的宽或高，单位为毫米，必须为正数。与左下角 X、Y 共同定义区域，X+W、Y+H 不得超出地图边界。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+进入撤离区后需要连续保持的 Tick 数，60 Tick=1 秒。离开区域、受到正伤害或死亡会清零，暂停冻结计时。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用同地图 MonsterSpawn.SpawnIdx，指定要击败的具体 Boss 出生实例，不是 MonsterIdx。本历史首版要求该出生关联 Rank=2 的怪物，且必须有实际 Boss 引用，0 不适用于此回归入口。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 Player 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+角色碰撞体尺寸，单位为毫米，必须为正偶数。出生点按脚底中心定位，偶数尺寸保证半宽等几何运算保持整数。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+角色碰撞体尺寸，单位为毫米，必须为正偶数。出生点按脚底中心定位，偶数尺寸保证半宽等几何运算保持整数。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+每个 Tick 的移动距离，单位为毫米/Tick。固定 60 Tick/秒，例如 100 对应每秒 6000 毫米。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+起跳时向上的初速度，单位为毫米/Tick。后续速度由地图 Gravity 按 Tick 递减，不能将此值直接当作跳跃高度。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/fieldNotes9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+本行记录在 Monster 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。本工作簿为冻结的旧首版回归内容，不跟随当前正式表调参。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+历史首版使用 1=普通怪、2=Boss。此枚举用于旧回归出口资格，不能套用当前根目录正式表的 2=精英、3=Boss。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+角色碰撞体尺寸，单位为毫米，必须为正偶数。出生点按脚底中心定位，偶数尺寸保证半宽等几何运算保持整数。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+角色碰撞体尺寸，单位为毫米，必须为正偶数。出生点按脚底中心定位，偶数尺寸保证半宽等几何运算保持整数。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+每个 Tick 的移动距离，单位为毫米/Tick。固定 60 Tick/秒，例如 100 对应每秒 6000 毫米。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Drop.DropIdx，由 DropEntry 中相同 DropIdx 的多行共同组成掉落组。一个组可被多个怪物复用。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -291,177 +1074,178 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>道具ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>道具名称</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>icon编号</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>道具大类</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>道具小类</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>道具子类</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>道具说明</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>堆叠上限</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="4" t="str">
+      <x:c r="C2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="str">
+      <x:c r="D2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="H2" s="4" t="str">
+      <x:c r="H2" s="7" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>ItemIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>IconId</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>Kind</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
+      <x:c r="F3" s="7" t="str">
         <x:v>SubType</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="str">
+      <x:c r="G3" s="7" t="str">
         <x:v>Desc</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="str">
+      <x:c r="H3" s="7" t="str">
         <x:v>MaxStack</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="str">
+      <x:c r="D4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="H4" s="4" t="str">
+      <x:c r="H4" s="7" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>100000001</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str">
+      <x:c r="B5" s="8" t="str">
         <x:v>训练步枪（示例）</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="str"/>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="C5" s="8" t="str"/>
+      <x:c r="D5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="n">
+      <x:c r="F5" s="8" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G5" s="5" t="str"/>
-      <x:c r="H5" s="5" t="n">
+      <x:c r="G5" s="8" t="str"/>
+      <x:c r="H5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="5" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>2800001</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="str">
+      <x:c r="B6" s="8" t="str">
         <x:v>废铁（示例）</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="str"/>
-      <x:c r="D6" s="5" t="n">
+      <x:c r="C6" s="8" t="str"/>
+      <x:c r="D6" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E6" s="5" t="n">
+      <x:c r="E6" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F6" s="5" t="n">
+      <x:c r="F6" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="5" t="str"/>
-      <x:c r="H6" s="5" t="n">
+      <x:c r="G6" s="8" t="str"/>
+      <x:c r="H6" s="8" t="n">
         <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="5" t="n">
+      <x:c r="A7" s="8" t="n">
         <x:v>2800002</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="str">
+      <x:c r="B7" s="8" t="str">
         <x:v>首领徽记（示例）</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="str"/>
-      <x:c r="D7" s="5" t="n">
+      <x:c r="C7" s="8" t="str"/>
+      <x:c r="D7" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="5" t="n">
+      <x:c r="E7" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="5" t="n">
+      <x:c r="F7" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G7" s="5" t="str"/>
-      <x:c r="H7" s="5" t="n">
+      <x:c r="G7" s="8" t="str"/>
+      <x:c r="H7" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -476,91 +1260,92 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>技能绑定ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>怪物配置ID</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>技能ID</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>使用优先级</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="C2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>BindIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>MonsterIdx</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>SkillIdx</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>Priority</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="n">
+      <x:c r="B5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="C5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="5" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="n">
+      <x:c r="B6" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="n">
+      <x:c r="C6" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="n">
+      <x:c r="D6" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -577,107 +1362,108 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>武器配置ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>名称</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>攻击技能ID</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>弹匣容量</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>初始备弹</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>换弹时间（Tick）</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
+      <x:c r="C2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>WeaponIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>AttackSkillIdx</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>Magazine</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>InitialReserve</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
+      <x:c r="F3" s="7" t="str">
         <x:v>ReloadTicks</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str">
+      <x:c r="B5" s="8" t="str">
         <x:v>灰盒步枪</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="C5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="n">
+      <x:c r="F5" s="8" t="n">
         <x:v>90</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -701,264 +1487,265 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>技能ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>名称</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>技能说明</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>施放类型</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>攻击距离（毫米）</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>基础伤害</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>冷却（Tick）</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>前摇（Tick）</x:v>
       </x:c>
-      <x:c r="I1" s="3" t="str">
+      <x:c r="I1" s="6" t="str">
         <x:v>后摇（Tick）</x:v>
       </x:c>
-      <x:c r="J1" s="3" t="str">
+      <x:c r="J1" s="6" t="str">
         <x:v>技能图标</x:v>
       </x:c>
-      <x:c r="K1" s="3" t="str">
+      <x:c r="K1" s="6" t="str">
         <x:v>动画资源</x:v>
       </x:c>
-      <x:c r="L1" s="3" t="str">
+      <x:c r="L1" s="6" t="str">
         <x:v>特效资源</x:v>
       </x:c>
-      <x:c r="M1" s="3" t="str">
+      <x:c r="M1" s="6" t="str">
         <x:v>音效资源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="4" t="str">
+      <x:c r="C2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="H2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="I2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="J2" s="4" t="str">
+      <x:c r="D2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="I2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="J2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="K2" s="4" t="str">
+      <x:c r="K2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="L2" s="4" t="str">
+      <x:c r="L2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="M2" s="4" t="str">
+      <x:c r="M2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>SkillIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>Desc</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>CastType</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>Range</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
+      <x:c r="F3" s="7" t="str">
         <x:v>Damage</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="str">
+      <x:c r="G3" s="7" t="str">
         <x:v>CooldownTicks</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="str">
+      <x:c r="H3" s="7" t="str">
         <x:v>WindupTicks</x:v>
       </x:c>
-      <x:c r="I3" s="4" t="str">
+      <x:c r="I3" s="7" t="str">
         <x:v>RecoveryTicks</x:v>
       </x:c>
-      <x:c r="J3" s="4" t="str">
+      <x:c r="J3" s="7" t="str">
         <x:v>IconId</x:v>
       </x:c>
-      <x:c r="K3" s="4" t="str">
+      <x:c r="K3" s="7" t="str">
         <x:v>AnimId</x:v>
       </x:c>
-      <x:c r="L3" s="4" t="str">
+      <x:c r="L3" s="7" t="str">
         <x:v>EffectId</x:v>
       </x:c>
-      <x:c r="M3" s="4" t="str">
+      <x:c r="M3" s="7" t="str">
         <x:v>SoundId</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="I4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="J4" s="4" t="str">
+      <x:c r="D4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="K4" s="4" t="str">
+      <x:c r="K4" s="7" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="L4" s="4" t="str">
+      <x:c r="L4" s="7" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="M4" s="4" t="str">
+      <x:c r="M4" s="7" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str">
+      <x:c r="B5" s="8" t="str">
         <x:v>灰盒射击</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="str"/>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="C5" s="8" t="str"/>
+      <x:c r="D5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="n">
+      <x:c r="F5" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G5" s="5" t="n">
+      <x:c r="G5" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H5" s="5" t="n">
+      <x:c r="H5" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I5" s="5" t="n">
+      <x:c r="I5" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J5" s="5" t="str"/>
-      <x:c r="K5" s="5" t="str"/>
-      <x:c r="L5" s="5" t="str"/>
-      <x:c r="M5" s="5" t="str"/>
+      <x:c r="J5" s="8" t="str"/>
+      <x:c r="K5" s="8" t="str"/>
+      <x:c r="L5" s="8" t="str"/>
+      <x:c r="M5" s="8" t="str"/>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="5" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="str">
+      <x:c r="B6" s="8" t="str">
         <x:v>灰盒近战</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="str"/>
-      <x:c r="D6" s="5" t="n">
+      <x:c r="C6" s="8" t="str"/>
+      <x:c r="D6" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E6" s="5" t="n">
+      <x:c r="E6" s="8" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="F6" s="5" t="n">
+      <x:c r="F6" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G6" s="5" t="n">
+      <x:c r="G6" s="8" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H6" s="5" t="n">
+      <x:c r="H6" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I6" s="5" t="n">
+      <x:c r="I6" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="5" t="str"/>
-      <x:c r="K6" s="5" t="str"/>
-      <x:c r="L6" s="5" t="str"/>
-      <x:c r="M6" s="5" t="str"/>
+      <x:c r="J6" s="8" t="str"/>
+      <x:c r="K6" s="8" t="str"/>
+      <x:c r="L6" s="8" t="str"/>
+      <x:c r="M6" s="8" t="str"/>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="5" t="n">
+      <x:c r="A7" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="str">
+      <x:c r="B7" s="8" t="str">
         <x:v>重击（示例）</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="str"/>
-      <x:c r="D7" s="5" t="n">
+      <x:c r="C7" s="8" t="str"/>
+      <x:c r="D7" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E7" s="5" t="n">
+      <x:c r="E7" s="8" t="n">
         <x:v>1500</x:v>
       </x:c>
-      <x:c r="F7" s="5" t="n">
+      <x:c r="F7" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G7" s="5" t="n">
+      <x:c r="G7" s="8" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="H7" s="5" t="n">
+      <x:c r="H7" s="8" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="I7" s="5" t="n">
+      <x:c r="I7" s="8" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="J7" s="5" t="str"/>
-      <x:c r="K7" s="5" t="str"/>
-      <x:c r="L7" s="5" t="str"/>
-      <x:c r="M7" s="5" t="str"/>
+      <x:c r="J7" s="8" t="str"/>
+      <x:c r="K7" s="8" t="str"/>
+      <x:c r="L7" s="8" t="str"/>
+      <x:c r="M7" s="8" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -971,55 +1758,56 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>掉落组ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>名称</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>DropIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>Name</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str">
+      <x:c r="B5" s="8" t="str">
         <x:v>普通怪掉落（示例）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="5" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="str">
+      <x:c r="B6" s="8" t="str">
         <x:v>首领掉落（示例）</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -1036,147 +1824,148 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>掉落明细ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>掉落组ID</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>道具ID</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>概率（万分比）</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>最少数量</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>最多数量</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="C2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>EntryIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>DropIdx</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>ItemIdx</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>ChanceBp</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>MinCount</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
+      <x:c r="F3" s="7" t="str">
         <x:v>MaxCount</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="n">
+      <x:c r="B5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="C5" s="8" t="n">
         <x:v>2800001</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="n">
+      <x:c r="F5" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="5" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="n">
+      <x:c r="B6" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="n">
+      <x:c r="C6" s="8" t="n">
         <x:v>2800002</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="n">
+      <x:c r="D6" s="8" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="E6" s="5" t="n">
+      <x:c r="E6" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F6" s="5" t="n">
+      <x:c r="F6" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="5" t="n">
+      <x:c r="A7" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="n">
+      <x:c r="B7" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="n">
+      <x:c r="C7" s="8" t="n">
         <x:v>2800001</x:v>
       </x:c>
-      <x:c r="D7" s="5" t="n">
+      <x:c r="D7" s="8" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="E7" s="5" t="n">
+      <x:c r="E7" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F7" s="5" t="n">
+      <x:c r="F7" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -1190,62 +1979,63 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>配置ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>格数</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>拾取半径（毫米）</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="C2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>BagIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>Slots</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>PickupRadius</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="n">
+      <x:c r="B5" s="8" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="C5" s="8" t="n">
         <x:v>1500</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -1261,90 +2051,91 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>装备ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>装备名称</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>装备位置</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>武器类型</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>武器配置ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="str">
+      <x:c r="C2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>ItemIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>EquipPos</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>WeaponType</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>WeaponIdx</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
         <x:v>client/index</x:v>
       </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
+      <x:c r="C4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
         <x:v>client/server</x:v>
       </x:c>
-      <x:c r="E4" s="4" t="str">
+      <x:c r="E4" s="7" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>100000001</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str"/>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="B5" s="8" t="str"/>
+      <x:c r="C5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -1362,120 +2153,121 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>地图ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>名称</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>地图模式</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>地图宽度（毫米）</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>地图高度（毫米）</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>重力（毫米/Tick²）</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>场景资源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="str">
+      <x:c r="C2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>MapIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>Mode</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>Width</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>Height</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
+      <x:c r="F3" s="7" t="str">
         <x:v>Gravity</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="str">
+      <x:c r="G3" s="7" t="str">
         <x:v>SceneId</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str">
+      <x:c r="B5" s="8" t="str">
         <x:v>撤离演示（示例）</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="C5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>24000</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="n">
+      <x:c r="F5" s="8" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G5" s="5" t="str"/>
+      <x:c r="G5" s="8" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -1492,147 +2284,148 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>碰撞块ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>地图ID</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>X（毫米）</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>Y（毫米）</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>宽（毫米）</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>高（毫米）</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="C2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>SolidIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>MapIdx</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>W</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
+      <x:c r="F3" s="7" t="str">
         <x:v>H</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="n">
+      <x:c r="B5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="C5" s="8" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="n">
+      <x:c r="F5" s="8" t="n">
         <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="5" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="n">
+      <x:c r="B6" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="n">
+      <x:c r="C6" s="8" t="n">
         <x:v>8500</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="n">
+      <x:c r="D6" s="8" t="n">
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="E6" s="5" t="n">
+      <x:c r="E6" s="8" t="n">
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="F6" s="5" t="n">
+      <x:c r="F6" s="8" t="n">
         <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="5" t="n">
+      <x:c r="A7" s="8" t="n">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="n">
+      <x:c r="B7" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="n">
+      <x:c r="C7" s="8" t="n">
         <x:v>15000</x:v>
       </x:c>
-      <x:c r="D7" s="5" t="n">
+      <x:c r="D7" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E7" s="5" t="n">
+      <x:c r="E7" s="8" t="n">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="F7" s="5" t="n">
+      <x:c r="F7" s="8" t="n">
         <x:v>1000</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -1649,107 +2442,108 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>玩家出生ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>地图ID</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>玩家配置ID</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>初始装备道具ID</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>X（毫米）</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>Y（毫米）</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="C2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>SpawnIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>MapIdx</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>PlayerIdx</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>EquipItemIdx</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
+      <x:c r="F3" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="n">
+      <x:c r="B5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="C5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>100000001</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="n">
+      <x:c r="F5" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -1767,168 +2561,169 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>怪物出生ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>地图ID</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>怪物配置ID</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>X（毫米）</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>Y（毫米）</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>巡逻左端（毫米）</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>巡逻右端（毫米）</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="C2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>SpawnIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>MapIdx</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>MonsterIdx</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
+      <x:c r="F3" s="7" t="str">
         <x:v>PatrolMin</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="str">
+      <x:c r="G3" s="7" t="str">
         <x:v>PatrolMax</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="n">
+      <x:c r="B5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="C5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="n">
+      <x:c r="F5" s="8" t="n">
         <x:v>11000</x:v>
       </x:c>
-      <x:c r="G5" s="5" t="n">
+      <x:c r="G5" s="8" t="n">
         <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="5" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="n">
+      <x:c r="B6" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="n">
+      <x:c r="C6" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="n">
+      <x:c r="D6" s="8" t="n">
         <x:v>19000</x:v>
       </x:c>
-      <x:c r="E6" s="5" t="n">
+      <x:c r="E6" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F6" s="5" t="n">
+      <x:c r="F6" s="8" t="n">
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="G6" s="5" t="n">
+      <x:c r="G6" s="8" t="n">
         <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="5" t="n">
+      <x:c r="A7" s="8" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="n">
+      <x:c r="B7" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="n">
+      <x:c r="C7" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="5" t="n">
+      <x:c r="D7" s="8" t="n">
         <x:v>22800</x:v>
       </x:c>
-      <x:c r="E7" s="5" t="n">
+      <x:c r="E7" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="5" t="n">
+      <x:c r="F7" s="8" t="n">
         <x:v>21700</x:v>
       </x:c>
-      <x:c r="G7" s="5" t="n">
+      <x:c r="G7" s="8" t="n">
         <x:v>23200</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -1947,137 +2742,138 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>撤离点ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>地图ID</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>X（毫米）</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>Y（毫米）</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>区域宽（毫米）</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>区域高（毫米）</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>撤离读条（Tick）</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>所需Boss出生ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="C2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="H2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
         <x:v>int32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>ExtractIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>MapIdx</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>Y</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>W</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
+      <x:c r="F3" s="7" t="str">
         <x:v>H</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="str">
+      <x:c r="G3" s="7" t="str">
         <x:v>HoldTicks</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="str">
+      <x:c r="H3" s="7" t="str">
         <x:v>NeedBossSpawnIdx</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="str">
         <x:v>server/client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="n">
+      <x:c r="B5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="C5" s="8" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="n">
+      <x:c r="F5" s="8" t="n">
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="G5" s="5" t="n">
+      <x:c r="G5" s="8" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H5" s="5" t="n">
+      <x:c r="H5" s="8" t="n">
         <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -2096,135 +2892,136 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>玩家配置ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>名称</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>碰撞宽度（毫米）</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>碰撞高度（毫米）</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>最大生命</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>移速（毫米/Tick）</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>跳跃速度（毫米/Tick）</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>角色资源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="H2" s="4" t="str">
+      <x:c r="C2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>PlayerIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>Width</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>Height</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>Hp</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
+      <x:c r="F3" s="7" t="str">
         <x:v>Speed</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="str">
+      <x:c r="G3" s="7" t="str">
         <x:v>JumpSpeed</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="str">
+      <x:c r="H3" s="7" t="str">
         <x:v>PrefabId</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str">
+      <x:c r="B5" s="8" t="str">
         <x:v>撤离玩家（示例）</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="C5" s="8" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>1600</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="n">
+      <x:c r="F5" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G5" s="5" t="n">
+      <x:c r="G5" s="8" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="H5" s="5" t="str"/>
+      <x:c r="H5" s="8" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>
 
@@ -2245,194 +3042,195 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="6" t="str">
         <x:v>怪物配置ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>名称</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>怪物分类</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>碰撞宽度（毫米）</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>碰撞高度（毫米）</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>最大生命</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>移速（毫米/Tick）</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>警戒范围（毫米）</x:v>
       </x:c>
-      <x:c r="I1" s="3" t="str">
+      <x:c r="I1" s="6" t="str">
         <x:v>掉落组ID</x:v>
       </x:c>
-      <x:c r="J1" s="3" t="str">
+      <x:c r="J1" s="6" t="str">
         <x:v>怪物资源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
+      <x:c r="A2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="H2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="I2" s="4" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="J2" s="4" t="str">
+      <x:c r="C2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="I2" s="7" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="J2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>MonsterIdx</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>Rank</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>Width</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>Height</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
+      <x:c r="F3" s="7" t="str">
         <x:v>Hp</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="str">
+      <x:c r="G3" s="7" t="str">
         <x:v>Speed</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="str">
+      <x:c r="H3" s="7" t="str">
         <x:v>DetectRange</x:v>
       </x:c>
-      <x:c r="I3" s="4" t="str">
+      <x:c r="I3" s="7" t="str">
         <x:v>DropIdx</x:v>
       </x:c>
-      <x:c r="J3" s="4" t="str">
+      <x:c r="J3" s="7" t="str">
         <x:v>PrefabId</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="7" t="str">
         <x:v>server/client/key</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="I4" s="4" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="J4" s="4" t="str">
+      <x:c r="B4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="str">
+        <x:v>server/client</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="5" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str">
+      <x:c r="B5" s="8" t="str">
         <x:v>拾荒兽（示例）</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="C5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>1400</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="n">
+      <x:c r="F5" s="8" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G5" s="5" t="n">
+      <x:c r="G5" s="8" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H5" s="5" t="n">
+      <x:c r="H5" s="8" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="I5" s="5" t="n">
+      <x:c r="I5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J5" s="5" t="str"/>
+      <x:c r="J5" s="8" t="str"/>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="5" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="str">
+      <x:c r="B6" s="8" t="str">
         <x:v>铁甲首领（示例）</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="n">
+      <x:c r="C6" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="n">
+      <x:c r="D6" s="8" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="E6" s="5" t="n">
+      <x:c r="E6" s="8" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="F6" s="5" t="n">
+      <x:c r="F6" s="8" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="G6" s="5" t="n">
+      <x:c r="G6" s="8" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H6" s="5" t="n">
+      <x:c r="H6" s="8" t="n">
         <x:v>7000</x:v>
       </x:c>
-      <x:c r="I6" s="5" t="n">
+      <x:c r="I6" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J6" s="5" t="str"/>
+      <x:c r="J6" s="8" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
 </x:worksheet>
 </file>